--- a/docs/资产清单_v4_真实数据.xlsx
+++ b/docs/资产清单_v4_真实数据.xlsx
@@ -19,16 +19,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统数据流表" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'边界数据流表'!$A$1:$G$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'边界接口表'!$A$1:$I$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'边界数据流表'!$A$1:$H$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'边界接口表'!$A$1:$I$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'数据资产'!$A$1:$H$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'域属性表'!$A$1:$E$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'功能资产'!$A$1:$C$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'支持资产'!$A$1:$E$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'支持资产'!$A$1:$E$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'STRIDE映射表'!$A$1:$E$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'信任边界表'!$A$1:$F$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'威胁主体表'!$A$1:$D$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'系统数据流表'!$A$1:$F$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'系统数据流表'!$A$1:$F$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -553,6 +553,7 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -591,6 +592,11 @@
           <t>所属边界接口</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>是否进入内部传播</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -600,32 +606,37 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GNSS</t>
+          <t>指挥控制系统</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>NAVS</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>GNSS定位与时间信息</t>
+          <t>航空器航线、电子围栏、备降点数据</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>SENSOR</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>BI04</t>
+          <t>BI01</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -637,7 +648,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>GNSS</t>
+          <t>指挥控制系统</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -647,22 +658,27 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>RTK差分修正数据</t>
+          <t>用户登录结果、故障信息管理、摄像头数据流地址管理、气象信息管、飞行数据、音频数据</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>SENSOR</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>BI05</t>
+          <t>BI01</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -674,32 +690,37 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>环境视觉目标</t>
+          <t>指挥控制系统</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>DAAS</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>探测信息视频数据</t>
+          <t>航空器在线状态信息</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>SENSOR</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>F13</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>BI06</t>
+          <t>BI01</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -711,32 +732,38 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>环境激光反射目标</t>
+          <t>遥控器</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>DAAS</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>激光雷达点云数据</t>
+          <t>遥控器控制指令：
+滚转、俯仰、油门、偏航、模式、失控保护标志</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>SENSOR</t>
+          <t>CMD</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>F13</t>
+          <t>F7</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>BI06</t>
+          <t>BI03</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -748,32 +775,37 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>环境音频源</t>
+          <t>GNSS</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>AVCS</t>
+          <t>NAVS</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>环境语音与音频输入数据、机舱环境音频数据</t>
+          <t>GNSS定位与时间信息</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>SENSOR</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>F8</t>
+          <t>F4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>BI08</t>
+          <t>BI04</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -785,144 +817,164 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>GNSS</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>RTK差分修正数据</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>SENSOR</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>BI05</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BDF07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>环境激光反射目标</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>DAAS</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>激光雷达点云数据</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>SENSOR</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>F13</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>BI06</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>BDF08</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>环境音频源</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>AVCS</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>环境语音与音频输入数据、机舱环境音频数据</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>F8</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>BI08</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>BDF09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>环境视频目标</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>AVCS</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>舱内摄像头视频流
 下视摄像头视频数据</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>F8</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>BI08</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>BDF07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>DLS</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>地面维护设备</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>日志数据</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>F11</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>BI13</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>BDF08</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>ICCP</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>地面维护设备</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>诊断数据、日志数据</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>DATA</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
-        <is>
-          <t>F11</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>BI10</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>BDF09</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>ICCP</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>地面维护设备</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>软件版本与配置状态</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>STATE</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>F11</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>BI10</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -934,32 +986,37 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>环境视频目标</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>地面维护设备</t>
+          <t>DAAS</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>电推进周期性状态数据</t>
+          <t>探测信息视频数据</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>SENSOR</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>F13</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>BI14</t>
+          <t>BI06</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -971,32 +1028,37 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>PACKS</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>地面维护设备</t>
+          <t>指挥控制系统</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1#和2#动力电池周期性状态数据</t>
+          <t>飞行数据、音频数据、视频数据</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>BI15</t>
+          <t>BI02</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1070,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>PACKS</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1018,12 +1080,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>动力电池告警信息</t>
+          <t>日志数据</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1033,7 +1095,12 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>BI15</t>
+          <t>BI13</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1045,7 +1112,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>PACKS</t>
+          <t>IMS</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1055,7 +1122,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>日志数据</t>
+          <t>诊断数据、日志数据</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1070,7 +1137,12 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>BI15</t>
+          <t>BI10</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1154,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>DAAS</t>
+          <t>IMS</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1092,12 +1164,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>日志数据</t>
+          <t>软件版本与配置状态</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -1107,7 +1179,12 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>BI18</t>
+          <t>BI10</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1119,7 +1196,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>AVCS</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1129,22 +1206,27 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>AVCS运行数据备份</t>
+          <t>电推进周期性状态数据</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>STATE</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>F10,F11</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>BI19</t>
+          <t>BI14</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1156,257 +1238,292 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>1#和2#动力电池周期性状态数据</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>BI15</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>BDF17</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>动力电池告警信息</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>ALERT</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>BI15</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>BDF18</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>日志数据</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>BI15</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>BDF19</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>DAAS</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>日志数据</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>BI18</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>BDF20</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>AVCS</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>AVCS运行数据备份</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>DATA</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>F10,F11</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>BI19</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>BDF21</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>PES</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
         <is>
           <t>地面维护设备</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>日志数据（UART接口）
 反馈软件升级结果（SWD接口）</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>F11</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>BI22</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>BDF17</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>BDF22</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>RCS</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>地面维护设备</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>操控单元的日志数据
 RTK基准站日志数据与统计信息
 席位计算机的音视频数据导出</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>F10,F11</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>BI24</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>BDF18</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>地面维护设备</t>
-        </is>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>IMS</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>管理软件/引导加载软件</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>LOAD</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>F11</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>BI10</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>BDF19</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>地面维护设备</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>FMS</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>管理软件/引导加载软件</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>LOAD</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>F11</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>BI11</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>BDF20</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>地面维护设备</t>
-        </is>
-      </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>FCS</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>管理软件/引导加载软件</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>LOAD</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>F11</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>BI12</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>BDF21</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>地面维护设备</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>IMS</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>软件维护配置</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>F2,F3,F11</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>BI10</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>BDF22</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>地面维护设备</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>FMS</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>软件维护配置</t>
-        </is>
-      </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>CONFIG</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t>F2,F3,F11</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t>BI11</t>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1418,32 +1535,37 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>地面维护设备</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>指挥控制系统</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>软件维护配置</t>
+          <t>用户账号密码、航空器航线、电子围栏、备降点数据、遥控站操作记录、故障信息存储、摄像头数据流地址存储、飞行数据存储、音频数据存储、视频数据存储</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>CONFIG</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>F2,F3,F11</t>
+          <t>F3</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>BI12</t>
+          <t>BI01</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1460,27 +1582,32 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>DLS</t>
+          <t>IMS</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>软件维护配置</t>
+          <t>管理软件/引导加载软件</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>CONFIG</t>
+          <t>LOAD</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>F8,F11</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>BI13</t>
+          <t>BI10</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1624,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>DLS</t>
+          <t>FMS</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1512,12 +1639,17 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>F8,F11</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>BI13</t>
+          <t>BI11</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1534,27 +1666,32 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>软件维护配置</t>
+          <t>管理软件/引导加载软件</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>CONFIG</t>
+          <t>LOAD</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>F1,F11</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>BI14</t>
+          <t>BI12</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1571,27 +1708,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EPS</t>
+          <t>IMS</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>管理软件/引导加载软件</t>
+          <t>软件维护配置</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>LOAD</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>F1,F11</t>
+          <t>F2,F3,F11</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>BI14</t>
+          <t>BI10</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1608,27 +1750,32 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>PACKS</t>
+          <t>FMS</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>管理软件/引导加载软件</t>
+          <t>软件维护配置</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>LOAD</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>F1,F9,F11</t>
+          <t>F2,F3,F11</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>BI15</t>
+          <t>BI11</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1645,27 +1792,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>HVDS</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>管理软件/引导加载软件</t>
+          <t>软件维护配置</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>LOAD</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>F1,F9,F11</t>
+          <t>F2,F3,F11</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>BI16</t>
+          <t>BI12</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1682,27 +1834,32 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>管理软件/引导加载软件</t>
+          <t>软件维护配置</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>LOAD</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>F1,F9,F11</t>
+          <t>F8,F11</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>BI17</t>
+          <t>BI13</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1719,27 +1876,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>DAAS</t>
+          <t>DLS</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>软件维护配置</t>
+          <t>管理软件/引导加载软件</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CONFIG</t>
+          <t>LOAD</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>F11,F13</t>
+          <t>F8,F11</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>BI18</t>
+          <t>BI13</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1756,27 +1918,32 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>DAAS</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>管理软件/引导加载软件</t>
+          <t>软件维护配置</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>LOAD</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>F11,F13</t>
+          <t>F1,F11</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>BI18</t>
+          <t>BI14</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1793,27 +1960,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>AVCS</t>
+          <t>EPS</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>软件维护配置</t>
+          <t>管理软件/引导加载软件</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>CONFIG</t>
+          <t>LOAD</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>F8,F11</t>
+          <t>F1,F11</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>BI19</t>
+          <t>BI14</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1830,27 +2002,32 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>AVCS</t>
+          <t>PACKS</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>诊断数据</t>
+          <t>管理软件/引导加载软件</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>LOAD</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>F8,F11</t>
+          <t>F1,F9,F11</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>BI19</t>
+          <t>BI15</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1867,7 +2044,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>AVCS</t>
+          <t>HVDS</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -1882,12 +2059,17 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>F8,F11</t>
+          <t>F1,F9,F11</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>BI19</t>
+          <t>BI16</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1904,7 +2086,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>NAVS</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -1919,12 +2101,17 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>F4,F11</t>
+          <t>F1,F9,F11</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>BI20</t>
+          <t>BI17</t>
+        </is>
+      </c>
+      <c r="H37" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1941,7 +2128,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>NAVS</t>
+          <t>DAAS</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -1956,12 +2143,17 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>F4,F11</t>
+          <t>F11,F13</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>BI20</t>
+          <t>BI18</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1978,12 +2170,12 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>PES</t>
+          <t>DAAS</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>管理软件/引导加载软件（SWD接口）</t>
+          <t>管理软件/引导加载软件</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -1993,12 +2185,17 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>F5,F11</t>
+          <t>F11,F13</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>BI22</t>
+          <t>BI18</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2212,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>PES</t>
+          <t>AVCS</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2030,12 +2227,17 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>F5,F11</t>
+          <t>F8,F11</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>BI22</t>
+          <t>BI19</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2052,12 +2254,12 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>PES</t>
+          <t>AVCS</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>诊断数据（UART接口）</t>
+          <t>诊断数据</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -2067,12 +2269,17 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>F5,F11</t>
+          <t>F8,F11</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>BI22</t>
+          <t>BI19</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2089,27 +2296,32 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>RCS</t>
+          <t>AVCS</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>诊断数据</t>
+          <t>管理软件/引导加载软件</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>LOAD</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>F8,F11</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>BI24</t>
+          <t>BI19</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2338,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>RCS</t>
+          <t>NAVS</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
@@ -2141,12 +2353,17 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>F4,F11</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>BI24</t>
+          <t>BI20</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2380,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>RCS</t>
+          <t>NAVS</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2178,12 +2395,17 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>F4,F11</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>BI24</t>
+          <t>BI20</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2200,12 +2422,12 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>RCS</t>
+          <t>PES</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>管理软件/引导加载软件</t>
+          <t>管理软件/引导加载软件（SWD接口）</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
@@ -2215,12 +2437,17 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>F5,F11</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>BI24</t>
+          <t>BI22</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2464,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>RCS</t>
+          <t>PES</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2252,12 +2479,17 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>F5,F11</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>BI24</t>
+          <t>BI22</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2269,17 +2501,17 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>操控员</t>
+          <t>地面维护设备</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>RCS</t>
+          <t>PES</t>
         </is>
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>人工控制输入</t>
+          <t>诊断数据（UART接口）</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -2289,12 +2521,17 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>F7</t>
+          <t>F5,F11</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>BI28</t>
+          <t>BI22</t>
+        </is>
+      </c>
+      <c r="H47" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2306,41 +2543,37 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
           <t>RCS</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>操控员</t>
-        </is>
-      </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>显示ACU状态数据
-显示航空器综合控制计算机状态，姿态，高度，速度，飞行状态，经纬度，遥控器，软硬件版本号周期性状态数据
-显示航空器1~12电动发动机周期性状态数据
-显示航空器1#和2#动力电池周期性状态数据
-显示航空器高压配电系统周期性状态数据
-显示航空器电气系统周期性状态数据
-显示航空器伞降系统周期性状态数据
-显示航空器导航系统周期性状态数据
-显示航空器探测与避让周期性状态数据
-显示航空器音视频通信系统周期性状态数据</t>
+          <t>诊断数据</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>STATE</t>
+          <t>DATA</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>F7</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>BI28</t>
+          <t>BI24</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2585,37 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
           <t>RCS</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>操控员</t>
-        </is>
-      </c>
       <c r="D49" s="3" t="inlineStr">
         <is>
-          <t>显示飞控，飞管，综管告警信息、电动发动机告警信息、动力电池系统告警信息、高压配电系统告警信息、电气系统告警信息、导航系统告警信息、探测与避让系统告警信息，音视频通信系统告警信息</t>
+          <t>管理软件/引导加载软件</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>ALERT</t>
+          <t>LOAD</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>F7</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>BI28</t>
+          <t>BI24</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2389,50 +2627,140 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
           <t>RCS</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>操控员</t>
-        </is>
-      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>乘员音频数据，下视摄像头视频数据，舱内摄像头视频流，探测信息视频数据</t>
+          <t>软件维护配置</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>DATA</t>
+          <t>CONFIG</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>F7,F8</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>BI28</t>
+          <t>BI24</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
+          <t>BDF50</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>管理软件/引导加载软件</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>LOAD</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>BI24</t>
+        </is>
+      </c>
+      <c r="H51" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>BDF51</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>地面维护设备</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>RCS</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>软件维护配置</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>CONFIG</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>F11</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>BI24</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
           <t>以下是样例，请勿填写此行以下内容</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr"/>
-      <c r="C51" s="3" t="inlineStr"/>
-      <c r="D51" s="3" t="inlineStr"/>
-      <c r="E51" s="3" t="inlineStr"/>
-      <c r="F51" s="3" t="inlineStr"/>
-      <c r="G51" s="3" t="inlineStr"/>
+      <c r="B53" s="3" t="inlineStr"/>
+      <c r="C53" s="3" t="inlineStr"/>
+      <c r="D53" s="3" t="inlineStr"/>
+      <c r="E53" s="3" t="inlineStr"/>
+      <c r="F53" s="3" t="inlineStr"/>
+      <c r="G53" s="3" t="inlineStr"/>
+      <c r="H53" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G51"/>
+  <autoFilter ref="A1:H53"/>
   <dataValidations count="1">
     <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CMD,CONFIG,STATE,DATA,LOAD,ALERT,SENSOR"</formula1>
@@ -2448,7 +2776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2672,7 +3000,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>遥控机接收器控制指令：
+          <t>遥控器控制指令：
 滚转、俯仰、油门、偏航、模式、失控保护标志</t>
         </is>
       </c>
@@ -2810,7 +3138,7 @@
 航空器伞降系统周期性状态数据
 航空器导航系统周期性状态数据
 航空器探测与避让周期性状态数据
-遥控器接收机周期性状态数据（显示油门、翻滚、俯仰、偏航）</t>
+遥控器周期性状态数据（显示油门、翻滚、俯仰、偏航）</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -2846,7 +3174,7 @@
 油门指令，滚转角指令，俯仰角指令，偏航角指令，1~12电机转速控制指令，横向控制量，纵向控制量，垂向控制量，偏航控制量
 飞控对遥控站控制指令的反馈数据
 航空器存储的航线，电子围栏，备降点数据
-遥控器接收器通道控制量显示（横向、纵向、垂向、偏航）</t>
+遥控器通道控制量显示（横向、纵向、垂向、偏航）</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -3050,7 +3378,7 @@
 航空器导航系统周期性状态数据
 航空器探测与避让周期性状态数据
 航空器音视频通信系统周期性状态数据
-遥控器接收机周期性状态数据（显示油门、翻滚、俯仰、偏航）</t>
+遥控器周期性状态数据（显示油门、翻滚、俯仰、偏航）</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3087,7 +3415,7 @@
 飞控对遥控站控制指令的反馈数据
 航空器存储的航线，电子围栏，备降点数据
 乘员音频数据，下视摄像头视频数据，舱内摄像头视频流，探测信息视频数据
-遥控器接收器通道控制量显示（横向、纵向、垂向、偏航）</t>
+遥控器通道控制量显示（横向、纵向、垂向、偏航）</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3346,7 +3674,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>遥控机接收器控制指令：
+          <t>遥控器控制指令：
 滚转、俯仰、油门、偏航、模式、失控保护标志</t>
         </is>
       </c>
@@ -4685,17 +5013,81 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
+          <t>SDF68</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>HVDS</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>12个电动发电机高压上下电指令</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>CMD</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>SDF69</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>PACKS</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>HVDS</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>1#和2#动力电池状态信息</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>STATE</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>F9</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
           <t>以下是样例，请勿填写此行以下内容</t>
         </is>
       </c>
-      <c r="B69" s="3" t="inlineStr"/>
-      <c r="C69" s="3" t="inlineStr"/>
-      <c r="D69" s="3" t="inlineStr"/>
-      <c r="E69" s="3" t="inlineStr"/>
-      <c r="F69" s="3" t="inlineStr"/>
+      <c r="B71" s="3" t="inlineStr"/>
+      <c r="C71" s="3" t="inlineStr"/>
+      <c r="D71" s="3" t="inlineStr"/>
+      <c r="E71" s="3" t="inlineStr"/>
+      <c r="F71" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F69"/>
+  <autoFilter ref="A1:F71"/>
   <dataValidations count="1">
     <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"CMD,CONFIG,STATE,DATA,LOAD,ALERT,SENSOR"</formula1>
@@ -4711,7 +5103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4832,17 +5224,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
+          <t>指挥控制系统</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
           <t>DLS</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>DLS</t>
-        </is>
-      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>4G/5G</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -4852,7 +5244,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>双向</t>
+          <t>单向</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -4862,7 +5254,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>转发航空器数据与遥控站数据</t>
+          <t>转发航空器数据至指挥控制系统</t>
         </is>
       </c>
     </row>
@@ -4879,7 +5271,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>遥控器接收机</t>
+          <t>遥控器</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -4909,7 +5301,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>遥控器接收机调试输入接口</t>
+          <t>遥控器调试接口</t>
         </is>
       </c>
     </row>
@@ -6044,67 +6436,20 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>BI28</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>人机交互</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>操控员</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>RCS</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>/</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>HMI</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>双向</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>SB-01</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>操控员交互接口</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
           <t>以下是样例，请勿填写此行以下内容</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr"/>
-      <c r="C30" s="2" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr"/>
-      <c r="E30" s="2" t="inlineStr"/>
-      <c r="F30" s="2" t="inlineStr"/>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="2" t="inlineStr"/>
+      <c r="B29" s="3" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr"/>
+      <c r="G29" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="inlineStr"/>
+      <c r="I29" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I30"/>
+  <autoFilter ref="A1:I29"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6994,7 +7339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7039,7 +7384,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GNSS</t>
+          <t>RCS</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr"/>
@@ -7062,18 +7407,18 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>NAVS</t>
+          <t>遥控器</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>External</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -7085,7 +7430,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>RCS</t>
+          <t>GNSS</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr"/>
@@ -7108,18 +7453,18 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>环境视觉目标</t>
+          <t>NAVS</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr"/>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7131,18 +7476,18 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>DAAS</t>
+          <t>环境激光反射目标</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Internal</t>
+          <t>External</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -7154,18 +7499,18 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>环境激光反射目标</t>
+          <t>DAAS</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>External</t>
+          <t>Internal</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7637,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ICCP</t>
+          <t>IMS</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr"/>
@@ -7384,7 +7729,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IMS</t>
+          <t>FMS</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
@@ -7407,7 +7752,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FMS</t>
+          <t>FCS</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr"/>
@@ -7430,7 +7775,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>FCS</t>
+          <t>HVDS</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr"/>
@@ -7453,7 +7798,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>HVDS</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr"/>
@@ -7471,62 +7816,16 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>ASA.20</t>
-        </is>
-      </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
+          <t>以下是样例，请勿填写此行以下内容</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr"/>
       <c r="C21" s="3" t="inlineStr"/>
-      <c r="D21" s="3" t="inlineStr">
-        <is>
-          <t>Internal</t>
-        </is>
-      </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>ASA.21</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>操控员</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>以下是样例，请勿填写此行以下内容</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr"/>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
+      <c r="D21" s="3" t="inlineStr"/>
+      <c r="E21" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E23"/>
+  <autoFilter ref="A1:E21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
